--- a/diseases/d054/1995-1999.xlsx
+++ b/diseases/d054/1995-1999.xlsx
@@ -716,17 +716,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -751,172 +751,101 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1995-01-01</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1997-01</t>
+          <t>1995-01</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>23</v>
+        <v>41087</v>
+      </c>
+      <c r="O2" t="n">
+        <v>41087</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Hlaupabóla</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 B01; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -948,12 +877,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -978,50 +907,53 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1997-02-01</t>
+          <t>1995-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1997-02</t>
+          <t>1995-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>28</v>
+        <v>41087</v>
+      </c>
+      <c r="O3" t="n">
+        <v>41087</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Hlaupabóla</t>
+          <t>Chickenpox</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>registered_diagnoses</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1031,7 +963,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1046,7 +978,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>not_comparable</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1056,7 +988,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1066,12 +998,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 B01; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1080,70 +1012,74 @@
         </is>
       </c>
       <c r="AN3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1106,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1205,172 +1141,101 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1997-03-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1997-03</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>36</v>
+        <v>20077</v>
+      </c>
+      <c r="O4" t="n">
+        <v>20077</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Hlaupabóla</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 B01; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1267,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1432,50 +1297,53 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1997-04-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1997-04</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>42</v>
+        <v>20077</v>
+      </c>
+      <c r="O5" t="n">
+        <v>20077</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Hlaupabóla</t>
+          <t>Chickenpox</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>registered_diagnoses</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1485,7 +1353,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1500,7 +1368,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>not_comparable</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1510,7 +1378,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1520,12 +1388,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 B01; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1534,70 +1402,74 @@
         </is>
       </c>
       <c r="AN5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1624,17 +1496,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1659,172 +1531,101 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1997-05-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1997-05</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>28866</v>
+      </c>
+      <c r="O6" t="n">
+        <v>28866</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Hlaupabóla</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 B01; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1856,12 +1657,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1886,50 +1687,53 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1997-06-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1997-06</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>39</v>
+        <v>28866</v>
+      </c>
+      <c r="O7" t="n">
+        <v>28866</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Hlaupabóla</t>
+          <t>Chickenpox</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>registered_diagnoses</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1939,7 +1743,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1954,7 +1758,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>not_comparable</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1964,7 +1768,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -1974,12 +1778,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 B01; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1988,70 +1792,74 @@
         </is>
       </c>
       <c r="AN7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -2113,16 +1921,16 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1997-07-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1997-07</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -2340,16 +2148,16 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1997-08-01</t>
+          <t>1997-02-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1997-08</t>
+          <t>1997-02</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -2567,16 +2375,16 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1997-09-01</t>
+          <t>1997-03-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1997-09</t>
+          <t>1997-03</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -2794,16 +2602,16 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1997-10-01</t>
+          <t>1997-04-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1997-10</t>
+          <t>1997-04</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -3021,16 +2829,16 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1997-11-01</t>
+          <t>1997-05-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1997-11</t>
+          <t>1997-05</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -3248,16 +3056,16 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1997-12-01</t>
+          <t>1997-06-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1997-12</t>
+          <t>1997-06</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -3475,16 +3283,16 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1997-07-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1997-07</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -3702,16 +3510,16 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1998-02-01</t>
+          <t>1997-08-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1998-02</t>
+          <t>1997-08</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -3929,16 +3737,16 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1998-03-01</t>
+          <t>1997-09-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1998-03</t>
+          <t>1997-09</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -4156,16 +3964,16 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1998-04-01</t>
+          <t>1997-10-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1998-04</t>
+          <t>1997-10</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -4383,16 +4191,16 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1998-05-01</t>
+          <t>1997-11-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1998-05</t>
+          <t>1997-11</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -4610,16 +4418,16 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1998-06-01</t>
+          <t>1997-12-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1998-06</t>
+          <t>1997-12</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -4802,17 +4610,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -4837,172 +4645,101 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1998-07-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1998-07</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>14</v>
+        <v>32024</v>
+      </c>
+      <c r="O20" t="n">
+        <v>32024</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>Hlaupabóla</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 B01; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr"/>
-      <c r="AT20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5034,12 +4771,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -5064,50 +4801,53 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1998-08-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1998-08</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>6</v>
+        <v>32024</v>
+      </c>
+      <c r="O21" t="n">
+        <v>32024</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Hlaupabóla</t>
+          <t>Chickenpox</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>registered_diagnoses</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -5117,7 +4857,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5132,7 +4872,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>not_comparable</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -5142,7 +4882,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
@@ -5152,12 +4892,12 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 B01; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -5166,70 +4906,74 @@
         </is>
       </c>
       <c r="AN21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5291,16 +5035,16 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1998-09-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1998-09</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -5518,16 +5262,16 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1998-10-01</t>
+          <t>1998-02-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1998-10</t>
+          <t>1998-02</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -5745,16 +5489,16 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1998-11-01</t>
+          <t>1998-03-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1998-11</t>
+          <t>1998-03</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>11</v>
+        <v>117</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -5972,16 +5716,16 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1998-12-01</t>
+          <t>1998-04-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1998-12</t>
+          <t>1998-04</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -6199,16 +5943,16 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1998-05-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1998-05</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -6391,17 +6135,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -6426,90 +6170,172 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1998-06-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1998-06</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>824</v>
-      </c>
-      <c r="O27" t="n">
-        <v>824</v>
-      </c>
-      <c r="Q27" t="n">
+        <v>28</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Hlaupabóla</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 B01; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN27" t="b">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -6571,16 +6397,16 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1998-07-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1998-07</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -6763,17 +6589,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -6798,90 +6624,172 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1998-08-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1998-08</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1625</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1625</v>
-      </c>
-      <c r="Q29" t="n">
+        <v>6</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Hlaupabóla</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 B01; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN29" t="b">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -6943,16 +6851,16 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1998-09-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1998-09</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -7135,17 +7043,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -7170,90 +7078,172 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1998-10-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1998-10</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1137</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1137</v>
-      </c>
-      <c r="Q31" t="n">
+        <v>25</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Hlaupabóla</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 B01; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN31" t="b">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -7315,16 +7305,16 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1998-11-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1998-11</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -7507,17 +7497,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -7542,90 +7532,172 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1998-12-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1998-12</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1322</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1322</v>
-      </c>
-      <c r="Q33" t="n">
+        <v>60</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Hlaupabóla</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 B01; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN33" t="b">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -7652,17 +7724,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -7687,172 +7759,101 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>75</v>
+        <v>24509</v>
+      </c>
+      <c r="O34" t="n">
+        <v>24509</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>Hlaupabóla</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 B01; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
-      <c r="AT34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV34" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7879,17 +7880,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -7914,90 +7915,179 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1652</v>
+        <v>24509</v>
       </c>
       <c r="O35" t="n">
-        <v>1652</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>24509</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN35" t="b">
+        <v>1</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D20_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8059,16 +8149,16 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -8286,19 +8376,19 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1999-07-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1365</v>
+        <v>824</v>
       </c>
       <c r="O37" t="n">
-        <v>1365</v>
+        <v>824</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -8431,16 +8521,16 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1999-07-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -8658,19 +8748,19 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
+          <t>1999-03-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>537</v>
+        <v>1625</v>
       </c>
       <c r="O39" t="n">
-        <v>537</v>
+        <v>1625</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -8803,16 +8893,16 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
+          <t>1999-03-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>18</v>
+        <v>114</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -9030,19 +9120,19 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1999-04-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>339</v>
+        <v>1137</v>
       </c>
       <c r="O41" t="n">
-        <v>339</v>
+        <v>1137</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -9175,16 +9265,16 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1999-04-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -9402,19 +9492,19 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1999-10-01</t>
+          <t>1999-05-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1999-10</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>479</v>
+        <v>1322</v>
       </c>
       <c r="O43" t="n">
-        <v>479</v>
+        <v>1322</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -9547,16 +9637,16 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1999-10-01</t>
+          <t>1999-05-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1999-10</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -9774,19 +9864,19 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1999-11-01</t>
+          <t>1999-06-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1999-11</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>810</v>
+        <v>1652</v>
       </c>
       <c r="O45" t="n">
-        <v>810</v>
+        <v>1652</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -9919,16 +10009,16 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1999-11-01</t>
+          <t>1999-06-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1999-11</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -10146,19 +10236,19 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-07-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1999-12</t>
+          <t>1999-07</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>800</v>
+        <v>1365</v>
       </c>
       <c r="O47" t="n">
-        <v>800</v>
+        <v>1365</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -10291,16 +10381,16 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-07-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1999-12</t>
+          <t>1999-07</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -10455,6 +10545,1866 @@
         </is>
       </c>
       <c r="BC48" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1999-08-01</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>1999-08</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>537</v>
+      </c>
+      <c r="O49" t="n">
+        <v>537</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>1999-08-01</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>1999-08</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>18</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Hlaupabóla</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 B01; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>1999-09-01</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>1999-09</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>339</v>
+      </c>
+      <c r="O51" t="n">
+        <v>339</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1999-09-01</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>1999-09</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>16</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Hlaupabóla</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 B01; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1999-10-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1999-10</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>479</v>
+      </c>
+      <c r="O53" t="n">
+        <v>479</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1999-10-01</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1999-10</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>20</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Hlaupabóla</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 B01; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1999-11-01</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1999-11</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>810</v>
+      </c>
+      <c r="O55" t="n">
+        <v>810</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>1999-11-01</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>1999-11</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>35</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Hlaupabóla</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 B01; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>1999-12-01</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>1999-12</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>800</v>
+      </c>
+      <c r="O57" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>1999-12-01</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>1999-12</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>65</v>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B01_HLAUPABOLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Hlaupabóla</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 B01; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
         <is>
           <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
@@ -10505,7 +12455,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1995-01-01</t>
         </is>
       </c>
     </row>
@@ -10576,7 +12526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -10586,7 +12536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -10606,7 +12556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -10616,7 +12566,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -10638,7 +12588,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10890</v>
+        <v>157453</v>
       </c>
     </row>
     <row r="16">
